--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486344_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486344_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.593</v>
+        <v>4.726</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9331</v>
+        <v>2.3743</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6599</v>
+        <v>2.3517</v>
       </c>
       <c r="G2" t="n">
         <v>3.5181</v>
@@ -610,13 +610,13 @@
         <v>0.87</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5105</v>
+        <v>0.6435</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1717</v>
+        <v>0.6129</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3389</v>
+        <v>0.0306</v>
       </c>
       <c r="V2" t="n">
         <v>1.8695</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7618</v>
+        <v>4.5075</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5021</v>
+        <v>4.2786</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2598</v>
+        <v>0.2289</v>
       </c>
       <c r="G3" t="n">
         <v>4.3398</v>
@@ -688,13 +688,13 @@
         <v>1.5225</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2725</v>
+        <v>1.0181</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.7427</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3063</v>
+        <v>0.2755</v>
       </c>
       <c r="V3" t="n">
         <v>-2.3729</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.6492</v>
+        <v>3.8575</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6966</v>
+        <v>2.2748</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9526</v>
+        <v>1.5827</v>
       </c>
       <c r="G4" t="n">
         <v>-0.1352</v>
@@ -766,13 +766,13 @@
         <v>0.6525</v>
       </c>
       <c r="S4" t="n">
-        <v>1.985</v>
+        <v>1.1933</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7487</v>
+        <v>0.3269</v>
       </c>
       <c r="U4" t="n">
-        <v>1.2363</v>
+        <v>0.8663999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>2.1469</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.766</v>
+        <v>2.0705</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6463</v>
+        <v>0.9816</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1197</v>
+        <v>1.0889</v>
       </c>
       <c r="G5" t="n">
         <v>-1.109</v>
@@ -844,13 +844,13 @@
         <v>1.305</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2655</v>
+        <v>0.5699</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1526</v>
+        <v>0.4879</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1128</v>
+        <v>0.082</v>
       </c>
       <c r="V5" t="n">
         <v>1.3045</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7211</v>
+        <v>1.8512</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0042</v>
+        <v>0.0727</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7168</v>
+        <v>1.7785</v>
       </c>
       <c r="G6" t="n">
         <v>-0.4143</v>
@@ -922,13 +922,13 @@
         <v>1.9576</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0277</v>
+        <v>1.1578</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8292</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1985</v>
+        <v>0.2602</v>
       </c>
       <c r="V6" t="n">
         <v>1.3252</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7998</v>
+        <v>1.6746</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1291</v>
+        <v>0.6532</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9288</v>
+        <v>1.0213</v>
       </c>
       <c r="G7" t="n">
         <v>0.0171</v>
@@ -1000,13 +1000,13 @@
         <v>1.5225</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7399</v>
+        <v>0.1349</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4675</v>
+        <v>0.3149</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2724</v>
+        <v>-0.18</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6363</v>
+        <v>0.0247</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9735</v>
+        <v>-0.8365</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3372</v>
+        <v>0.8612</v>
       </c>
       <c r="G8" t="n">
         <v>2.4288</v>
@@ -1078,13 +1078,13 @@
         <v>0.87</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5171</v>
+        <v>0.1439</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1899</v>
+        <v>-0.0529</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3272</v>
+        <v>0.1968</v>
       </c>
       <c r="V8" t="n">
         <v>-1.243</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9834000000000001</v>
+        <v>-1.201</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5508999999999999</v>
+        <v>0.2409</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5343</v>
+        <v>-1.4418</v>
       </c>
       <c r="G9" t="n">
         <v>1.612</v>
@@ -1156,13 +1156,13 @@
         <v>1.305</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8428</v>
+        <v>0.6252</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5432</v>
+        <v>0.2331</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2996</v>
+        <v>0.392</v>
       </c>
       <c r="V9" t="n">
         <v>-2.5682</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.1573</v>
+        <v>-3.9385</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1951</v>
+        <v>-1.7914</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9622</v>
+        <v>-2.1471</v>
       </c>
       <c r="G10" t="n">
         <v>-2.0601</v>
@@ -1234,13 +1234,13 @@
         <v>0.435</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2723</v>
+        <v>-0.0535</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.2812</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4127</v>
+        <v>0.2277</v>
       </c>
       <c r="V10" t="n">
         <v>-2.2599</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.1001</v>
+        <v>-4.4738</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.5474</v>
+        <v>-4.0751</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5527</v>
+        <v>-0.3986</v>
       </c>
       <c r="G11" t="n">
         <v>-2.1051</v>
@@ -1312,13 +1312,13 @@
         <v>0.435</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9043</v>
+        <v>-0.2779</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.3256</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1064</v>
+        <v>0.0478</v>
       </c>
       <c r="V11" t="n">
         <v>-1.4382</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.413800000000002</v>
+        <v>9.098700000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>3.488100000000001</v>
+        <v>4.173100000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>4.925599999999999</v>
+        <v>4.925700000000001</v>
       </c>
       <c r="G12" t="n">
         <v>6.0921</v>
@@ -1390,13 +1390,13 @@
         <v>10.8751</v>
       </c>
       <c r="S12" t="n">
-        <v>4.470400000000001</v>
+        <v>5.1552</v>
       </c>
       <c r="T12" t="n">
-        <v>2.2713</v>
+        <v>2.9564</v>
       </c>
       <c r="U12" t="n">
-        <v>2.1991</v>
+        <v>2.199</v>
       </c>
       <c r="V12" t="n">
         <v>-3.2361</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.3071</v>
+        <v>5.4433</v>
       </c>
       <c r="E13" t="n">
-        <v>4.4226</v>
+        <v>4.1991</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8845</v>
+        <v>1.2442</v>
       </c>
       <c r="G13" t="n">
         <v>-0.0281</v>
@@ -1468,13 +1468,13 @@
         <v>1.7401</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3374</v>
+        <v>-0.2013</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3953</v>
+        <v>-0.6189</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0579</v>
+        <v>0.4176</v>
       </c>
       <c r="V13" t="n">
         <v>4.1501</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7949</v>
+        <v>2.6826</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3675</v>
+        <v>0.9263</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4274</v>
+        <v>1.7562</v>
       </c>
       <c r="G14" t="n">
         <v>2.4929</v>
@@ -1546,13 +1546,13 @@
         <v>1.5225</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.1956</v>
+        <v>-0.3079</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0839</v>
+        <v>-0.5251</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1117</v>
+        <v>0.2172</v>
       </c>
       <c r="V14" t="n">
         <v>2.4552</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. TAMBA VILLEN</t>
+          <t>T. RICHARDSON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2751</v>
+        <v>-0.056</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.5471</v>
+        <v>-0.843</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2719</v>
+        <v>0.787</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.193</v>
+        <v>-0.8497</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.9762999999999999</v>
+        <v>-0.6083</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2168</v>
+        <v>-0.2415</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.6654</v>
+        <v>-1.1691</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.7419</v>
+        <v>-0.1579</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0765</v>
+        <v>-1.0112</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5276999999999999</v>
+        <v>0.3194</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2344</v>
+        <v>-0.4504</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2933</v>
+        <v>0.7697000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="R15" t="n">
         <v>1.0875</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3648</v>
+        <v>-0.07630000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0769</v>
+        <v>-0.5864</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2879</v>
+        <v>0.5101</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1952</v>
+        <v>1.13</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. RICHARDSON</t>
+          <t>I. TAMBA VILLEN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3669</v>
+        <v>-0.3381</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.0666</v>
+        <v>-0.8823</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6997</v>
+        <v>0.5442</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.8497</v>
+        <v>-1.193</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.6083</v>
+        <v>-0.9762999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2415</v>
+        <v>-0.2168</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.1691</v>
+        <v>-0.6654</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.1579</v>
+        <v>-0.7419</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.0112</v>
+        <v>0.0765</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3194</v>
+        <v>-0.5276999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4504</v>
+        <v>-0.2344</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7697000000000001</v>
+        <v>-0.2933</v>
       </c>
       <c r="P16" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>1.0875</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3872</v>
+        <v>-0.4278</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8099</v>
+        <v>-0.4122</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4227</v>
+        <v>-0.0156</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="W16" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. TORRES CUEVAS</t>
+          <t>S. LLORENTE PAZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8509</v>
+        <v>-0.783</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9622000000000001</v>
+        <v>-1.6896</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.8131</v>
+        <v>0.9066</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2706</v>
+        <v>-1.087</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0921</v>
+        <v>-0.9762999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.3626</v>
+        <v>-0.1108</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8356</v>
+        <v>-1.4336</v>
       </c>
       <c r="K17" t="n">
-        <v>1.5424</v>
+        <v>-0.7268</v>
       </c>
       <c r="L17" t="n">
         <v>-0.7068</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1062</v>
+        <v>0.3466</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4504</v>
+        <v>-0.2495</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6558</v>
+        <v>0.596</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2175</v>
+        <v>0.6525</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2021</v>
+        <v>-0.3485</v>
       </c>
       <c r="T17" t="n">
-        <v>0.08409999999999999</v>
+        <v>-0.256</v>
       </c>
       <c r="U17" t="n">
-        <v>0.118</v>
+        <v>-0.0925</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.695</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B. COULIBALY</t>
+          <t>M. TORRES CUEVAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9026999999999999</v>
+        <v>-0.9755</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9051</v>
+        <v>0.6269</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.8078</v>
+        <v>-1.6025</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7065</v>
+        <v>-0.2706</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3041</v>
+        <v>1.0921</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4024</v>
+        <v>-1.3626</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0944</v>
+        <v>0.8356</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0944</v>
+        <v>1.5424</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0.7068</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8008999999999999</v>
+        <v>-1.1062</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3985</v>
+        <v>-0.4504</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4024</v>
+        <v>-0.6558</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.87</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2175</v>
+        <v>0.87</v>
       </c>
       <c r="S18" t="n">
-        <v>2.1735</v>
+        <v>0.0775</v>
       </c>
       <c r="T18" t="n">
-        <v>2.6377</v>
+        <v>-0.2511</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4642</v>
+        <v>0.3287</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.4997</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.7395</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.7602</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. LLORENTE PAZ</t>
+          <t>U. MENDICOTE RUBIO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2788</v>
+        <v>-1.9618</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9131</v>
+        <v>-0.9053</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6343</v>
+        <v>-1.0565</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.087</v>
+        <v>-0.9263</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.9762999999999999</v>
+        <v>-1.3717</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1108</v>
+        <v>0.4454</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.4336</v>
+        <v>0.2604</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.7268</v>
+        <v>0.2222</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7068</v>
+        <v>0.0382</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3466</v>
+        <v>-1.1867</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2495</v>
+        <v>-1.5939</v>
       </c>
       <c r="O19" t="n">
-        <v>0.596</v>
+        <v>0.4072</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6525</v>
+        <v>-0.435</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8443000000000001</v>
+        <v>-0.426</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4795</v>
+        <v>-0.2511</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3648</v>
+        <v>-0.1749</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.1745</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.3904</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4599</v>
+        <v>-2.0064</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7805</v>
+        <v>-0.4453</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6794</v>
+        <v>-1.5612</v>
       </c>
       <c r="G20" t="n">
         <v>-0.1667</v>
@@ -2014,13 +2014,13 @@
         <v>0.435</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8581</v>
+        <v>-0.4047</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4795</v>
+        <v>-0.1442</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3787</v>
+        <v>-0.2605</v>
       </c>
       <c r="V20" t="n">
         <v>-0.5649999999999999</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>U. MENDICOTE RUBIO</t>
+          <t>J. MWEMA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6337</v>
+        <v>-2.0907</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4641</v>
+        <v>-1.5495</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1696</v>
+        <v>-0.5412</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9263</v>
+        <v>-1.2196</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3717</v>
+        <v>-0.9399</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4454</v>
+        <v>-0.2797</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2604</v>
+        <v>-0.6338</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2222</v>
+        <v>0.073</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0382</v>
+        <v>-0.7068</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1867</v>
+        <v>-0.5858</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.5939</v>
+        <v>-1.0129</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4072</v>
+        <v>0.4271</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.435</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.305</v>
+        <v>-1.0875</v>
       </c>
       <c r="R21" t="n">
         <v>0.87</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0979</v>
+        <v>0.1067</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8099</v>
+        <v>0.1719</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2879</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1745</v>
+        <v>-0.7602</v>
       </c>
       <c r="W21" t="n">
-        <v>0.3904</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. MWEMA</t>
+          <t>B. COULIBALY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.706</v>
+        <v>-2.6343</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1083</v>
+        <v>-0.883</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5977</v>
+        <v>-1.7513</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.2196</v>
+        <v>-0.7065</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9399</v>
+        <v>-0.3041</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2797</v>
+        <v>-0.4024</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6338</v>
+        <v>0.0944</v>
       </c>
       <c r="K22" t="n">
-        <v>0.073</v>
+        <v>0.0944</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7068</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5858</v>
+        <v>-0.8008999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0129</v>
+        <v>-0.3985</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4271</v>
+        <v>-0.4024</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.2175</v>
+        <v>-0.87</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R22" t="n">
-        <v>0.87</v>
+        <v>0.2175</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5087</v>
+        <v>0.4419</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3869</v>
+        <v>0.8496</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1217</v>
+        <v>-0.4077</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.7602</v>
+        <v>-1.4997</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X22" t="n">
         <v>-0.7602</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0417</v>
+        <v>-3.4586</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.7034</v>
+        <v>-3.4799</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3383</v>
+        <v>0.0213</v>
       </c>
       <c r="G23" t="n">
         <v>-2.1373</v>
@@ -2248,13 +2248,13 @@
         <v>0.435</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2519</v>
+        <v>-0.6687</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.399</v>
+        <v>-0.1754</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.853</v>
+        <v>-0.4933</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.413699999999999</v>
+        <v>-6.178500000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.9257</v>
+        <v>-4.9256</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.4881</v>
+        <v>-1.2532</v>
       </c>
       <c r="G24" t="n">
-        <v>-6.091900000000001</v>
+        <v>-6.091899999999999</v>
       </c>
       <c r="H24" t="n">
         <v>-7.283299999999999</v>
@@ -2326,13 +2326,13 @@
         <v>9.787599999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>-4.4703</v>
+        <v>-2.2351</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.199</v>
+        <v>-2.1989</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.2713</v>
+        <v>-0.03610000000000013</v>
       </c>
       <c r="V24" t="n">
         <v>3.2361</v>
